--- a/data/trans_orig/IP31KM11_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM11_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>116280</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>111030</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>119008</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>91,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>101041</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98454</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>99715</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>97072</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>124787</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>101859</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>131300</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>92,31%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>75,35%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>310</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>225829</t>
+          <t>215995</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204904</t>
+          <t>210572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232656</t>
+          <t>218850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4929</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10179</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10389</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3876</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>33317</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31982</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,74 +1063,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>92931</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>90776</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>95028</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>93434</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>93708</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>264</t>
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>186640</t>
+          <t>184908</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>184779</t>
+          <t>183312</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2616</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52891</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>47774</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55172</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>58665</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>52072</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>61590</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>83,54%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>148</t>
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>108753</t>
+          <t>104901</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101544</t>
+          <t>98792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111653</t>
+          <t>107174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2953</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3669</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>10262</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>16,46%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,74 +1749,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>193317</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>187670</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>195910</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>97,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>213954</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>209479</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>97,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>174909</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>171000</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>176640</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>208797</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>203249</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>211501</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>537</t>
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>422752</t>
+          <t>368226</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416950</t>
+          <t>362111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>425985</t>
+          <t>371291</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3996</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9643</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1583</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1731</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6058</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5640</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3861</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9409</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>142095</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>135903</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>144684</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>113092</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>109114</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>114796</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>156465</t>
+          <t>112924</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151953</t>
+          <t>108603</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>158520</t>
+          <t>114822</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>269557</t>
+          <t>255019</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264464</t>
+          <t>248468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272671</t>
+          <t>258328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2210,22 +2210,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>64494</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>60810</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>92,33%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>67152</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>64154</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>68394</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>93,12%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>68058</t>
+          <t>68514</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64738</t>
+          <t>64855</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68876</t>
+          <t>69880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>135209</t>
+          <t>133008</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131485</t>
+          <t>129129</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137117</t>
+          <t>135192</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1743</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4741</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>476</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>658957</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>649676</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>665197</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>97,52%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>638259</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>632719</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>641765</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>901</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>710480</t>
+          <t>603101</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>692275</t>
+          <t>597723</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>719317</t>
+          <t>606585</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1348739</t>
+          <t>1262058</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1326911</t>
+          <t>1251034</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1358627</t>
+          <t>1269575</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>16738</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>10498</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>26019</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>6872</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>3366</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>12412</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13051</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40093</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50588</t>
+          <t>34893</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
